--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -862,7 +862,7 @@
     <t>0.9930,0.0022,0.0016,0.0003</t>
   </si>
   <si>
-    <t>0.7354,0.0056,0.2369,0.0041</t>
+    <t>0.7354,0.0056,0.2368,0.0041</t>
   </si>
   <si>
     <t>0.0143,0.0126,0.9806,0.0020</t>
@@ -973,7 +973,7 @@
     <t>0.0002,0.0088,0.9991,0.0002</t>
   </si>
   <si>
-    <t>0.0011,0.3015,0.9832,0.0013</t>
+    <t>0.0011,0.3016,0.9831,0.0013</t>
   </si>
   <si>
     <t>0.0073,0.0015,0.9919,0.0015</t>
@@ -1093,7 +1093,7 @@
     <t>0.9760,0.0201,0.0037,0.0008</t>
   </si>
   <si>
-    <t>0.9643,0.0535,0.0008,0.0002</t>
+    <t>0.9644,0.0535,0.0008,0.0002</t>
   </si>
   <si>
     <t>0.9914,0.0101,0.0006,0.0003</t>
@@ -1309,7 +1309,7 @@
     <t>0.8612,0.0641,0.0601,0.0032</t>
   </si>
   <si>
-    <t>0.7077,0.0173,0.1992,0.0034</t>
+    <t>0.7078,0.0173,0.1992,0.0034</t>
   </si>
   <si>
     <t>0.9908,0.0061,0.0014,0.0005</t>
@@ -1393,7 +1393,7 @@
     <t>0.2041,0.0004,0.8696,0.0003</t>
   </si>
   <si>
-    <t>0.4641,0.0237,0.4558,0.0080</t>
+    <t>0.4642,0.0237,0.4557,0.0080</t>
   </si>
   <si>
     <t>0.0428,0.0100,0.9506,0.0034</t>
@@ -1408,7 +1408,7 @@
     <t>0.0966,0.0059,0.9036,0.0051</t>
   </si>
   <si>
-    <t>0.4923,0.0251,0.4249,0.0054</t>
+    <t>0.4923,0.0251,0.4248,0.0054</t>
   </si>
   <si>
     <t>0.0503,0.9734,0.0043,0.0002</t>
@@ -1438,7 +1438,7 @@
     <t>0.1726,0.0020,0.8201,0.0132</t>
   </si>
   <si>
-    <t>0.5176,0.0160,0.3615,0.0050</t>
+    <t>0.5176,0.0160,0.3614,0.0050</t>
   </si>
   <si>
     <t>0.0075,0.0006,0.9941,0.0005</t>
@@ -1531,7 +1531,7 @@
     <t>0.9907,0.0055,0.0016,0.0004</t>
   </si>
   <si>
-    <t>0.9159,0.0719,0.0074,0.0017</t>
+    <t>0.9160,0.0719,0.0074,0.0017</t>
   </si>
   <si>
     <t>0.9906,0.0022,0.0022,0.0003</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="525">
   <si>
     <t>Filename</t>
   </si>
@@ -817,6 +817,9 @@
     <t>0,0,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,0</t>
   </si>
   <si>
@@ -826,16 +829,19 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9339,0.0023,0.0178,0.0098</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9341,0.0023,0.0177,0.0097</t>
   </si>
   <si>
     <t>0.0039,0.0008,0.0004,0.9992</t>
   </si>
   <si>
-    <t>0.9517,0.0007,0.0003,0.0227</t>
-  </si>
-  <si>
-    <t>0.0872,0.0006,0.0020,0.9751</t>
+    <t>0.9518,0.0007,0.0003,0.0226</t>
+  </si>
+  <si>
+    <t>0.0874,0.0006,0.0020,0.9751</t>
   </si>
   <si>
     <t>0.9941,0.0016,0.0014,0.0003</t>
@@ -850,10 +856,10 @@
     <t>0.9932,0.0021,0.0014,0.0002</t>
   </si>
   <si>
-    <t>0.9619,0.0450,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9882,0.0095,0.0017,0.0009</t>
+    <t>0.9620,0.0449,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9883,0.0095,0.0017,0.0009</t>
   </si>
   <si>
     <t>0.9952,0.0017,0.0008,0.0002</t>
@@ -862,19 +868,19 @@
     <t>0.9930,0.0022,0.0016,0.0003</t>
   </si>
   <si>
-    <t>0.7354,0.0056,0.2368,0.0041</t>
+    <t>0.7365,0.0056,0.2357,0.0042</t>
   </si>
   <si>
     <t>0.0143,0.0126,0.9806,0.0020</t>
   </si>
   <si>
-    <t>0.2651,0.0007,0.8345,0.0002</t>
+    <t>0.2652,0.0007,0.8344,0.0002</t>
   </si>
   <si>
     <t>0.0463,0.0038,0.9593,0.0019</t>
   </si>
   <si>
-    <t>0.5519,0.0006,0.5444,0.0004</t>
+    <t>0.5524,0.0006,0.5438,0.0004</t>
   </si>
   <si>
     <t>0.0007,0.9989,0.0050,0.0009</t>
@@ -883,7 +889,7 @@
     <t>0.0019,0.9982,0.0030,0.0007</t>
   </si>
   <si>
-    <t>0.0082,0.9967,0.0013,0.0001</t>
+    <t>0.0083,0.9966,0.0013,0.0001</t>
   </si>
   <si>
     <t>0.0031,0.9959,0.0064,0.0027</t>
@@ -892,10 +898,10 @@
     <t>0.0007,0.9994,0.0045,0.0002</t>
   </si>
   <si>
-    <t>0.3017,0.0013,0.7259,0.0027</t>
-  </si>
-  <si>
-    <t>0.0557,0.0142,0.9216,0.0086</t>
+    <t>0.3022,0.0013,0.7254,0.0027</t>
+  </si>
+  <si>
+    <t>0.0558,0.0142,0.9215,0.0086</t>
   </si>
   <si>
     <t>0.0158,0.0003,0.9903,0.0003</t>
@@ -907,49 +913,49 @@
     <t>0.0123,0.0009,0.9908,0.0010</t>
   </si>
   <si>
-    <t>0.0313,0.0002,0.9812,0.0004</t>
+    <t>0.0314,0.0002,0.9812,0.0004</t>
   </si>
   <si>
     <t>0.0072,0.0002,0.9952,0.0003</t>
   </si>
   <si>
-    <t>0.5747,0.3648,0.0317,0.0041</t>
-  </si>
-  <si>
-    <t>0.9444,0.0567,0.0019,0.0010</t>
+    <t>0.5751,0.3645,0.0317,0.0041</t>
+  </si>
+  <si>
+    <t>0.9445,0.0566,0.0019,0.0010</t>
   </si>
   <si>
     <t>0.0016,0.0008,0.9988,0.0004</t>
   </si>
   <si>
-    <t>0.0146,0.1020,0.8980,0.0014</t>
+    <t>0.0146,0.1020,0.8981,0.0014</t>
   </si>
   <si>
     <t>0.9490,0.0063,0.0205,0.0013</t>
   </si>
   <si>
-    <t>0.9192,0.0264,0.0275,0.0014</t>
-  </si>
-  <si>
-    <t>0.3818,0.6903,0.0175,0.0031</t>
-  </si>
-  <si>
-    <t>0.0040,0.9480,0.6614,0.0014</t>
-  </si>
-  <si>
-    <t>0.0003,0.6373,0.9904,0.0001</t>
+    <t>0.9194,0.0264,0.0274,0.0014</t>
+  </si>
+  <si>
+    <t>0.3824,0.6897,0.0175,0.0031</t>
+  </si>
+  <si>
+    <t>0.0040,0.9480,0.6616,0.0014</t>
+  </si>
+  <si>
+    <t>0.0003,0.6374,0.9904,0.0001</t>
   </si>
   <si>
     <t>0.0035,0.0020,0.9956,0.0007</t>
   </si>
   <si>
-    <t>0.0364,0.0249,0.9330,0.0031</t>
-  </si>
-  <si>
-    <t>0.0529,0.0014,0.9407,0.0115</t>
-  </si>
-  <si>
-    <t>0.0008,0.3329,0.9865,0.0004</t>
+    <t>0.0363,0.0249,0.9331,0.0031</t>
+  </si>
+  <si>
+    <t>0.0530,0.0014,0.9406,0.0116</t>
+  </si>
+  <si>
+    <t>0.0008,0.3336,0.9865,0.0004</t>
   </si>
   <si>
     <t>0.0037,0.9948,0.0081,0.0003</t>
@@ -958,7 +964,7 @@
     <t>0.0053,0.0093,0.9897,0.0010</t>
   </si>
   <si>
-    <t>0.0007,0.8655,0.0006,0.9028</t>
+    <t>0.0007,0.8651,0.0006,0.9029</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0001,0.0000</t>
@@ -973,7 +979,7 @@
     <t>0.0002,0.0088,0.9991,0.0002</t>
   </si>
   <si>
-    <t>0.0011,0.3016,0.9831,0.0013</t>
+    <t>0.0011,0.3017,0.9832,0.0013</t>
   </si>
   <si>
     <t>0.0073,0.0015,0.9919,0.0015</t>
@@ -985,19 +991,19 @@
     <t>0.0114,0.0019,0.9904,0.0006</t>
   </si>
   <si>
-    <t>0.0155,0.0206,0.9593,0.0043</t>
-  </si>
-  <si>
-    <t>0.9613,0.0160,0.0139,0.0012</t>
-  </si>
-  <si>
-    <t>0.9711,0.0011,0.0182,0.0003</t>
+    <t>0.0155,0.0205,0.9593,0.0043</t>
+  </si>
+  <si>
+    <t>0.9613,0.0160,0.0138,0.0012</t>
+  </si>
+  <si>
+    <t>0.9712,0.0011,0.0182,0.0003</t>
   </si>
   <si>
     <t>0.9682,0.0139,0.0090,0.0063</t>
   </si>
   <si>
-    <t>0.1405,0.0021,0.8957,0.0012</t>
+    <t>0.1409,0.0021,0.8953,0.0012</t>
   </si>
   <si>
     <t>0.9847,0.0008,0.0072,0.0002</t>
@@ -1009,16 +1015,16 @@
     <t>0.9890,0.0019,0.0037,0.0002</t>
   </si>
   <si>
-    <t>0.0001,0.9972,0.8456,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0350,0.9986,0.0001</t>
+    <t>0.0001,0.9972,0.8457,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0351,0.9986,0.0001</t>
   </si>
   <si>
     <t>0.0016,0.0115,0.9947,0.0009</t>
   </si>
   <si>
-    <t>0.0003,0.9863,0.8262,0.0004</t>
+    <t>0.0003,0.9863,0.8263,0.0004</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9999,0.0001</t>
@@ -1030,22 +1036,22 @@
     <t>0.0003,0.9997,0.0011,0.0000</t>
   </si>
   <si>
-    <t>0.9413,0.0006,0.0473,0.0002</t>
-  </si>
-  <si>
-    <t>0.1216,0.0569,0.8444,0.0056</t>
+    <t>0.9415,0.0006,0.0471,0.0002</t>
+  </si>
+  <si>
+    <t>0.1217,0.0570,0.8442,0.0056</t>
   </si>
   <si>
     <t>0.0182,0.0088,0.9845,0.0017</t>
   </si>
   <si>
-    <t>0.0006,0.9591,0.8982,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.8615,0.9719,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0953,0.0000</t>
+    <t>0.0006,0.9591,0.8984,0.0006</t>
+  </si>
+  <si>
+    <t>0.0005,0.8616,0.9719,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0955,0.0000</t>
   </si>
   <si>
     <t>0.0003,0.9351,0.9493,0.0005</t>
@@ -1072,19 +1078,19 @@
     <t>0.0002,0.9957,0.8471,0.0001</t>
   </si>
   <si>
-    <t>0.0004,0.7242,0.9842,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.9701,0.4837,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.7998,0.9840,0.0003</t>
+    <t>0.0004,0.7244,0.9842,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.9701,0.4838,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.8000,0.9840,0.0003</t>
   </si>
   <si>
     <t>0.0001,0.9934,0.9270,0.0001</t>
   </si>
   <si>
-    <t>0.0004,0.9963,0.3016,0.0002</t>
+    <t>0.0004,0.9963,0.3017,0.0002</t>
   </si>
   <si>
     <t>0.9934,0.0069,0.0005,0.0003</t>
@@ -1093,7 +1099,7 @@
     <t>0.9760,0.0201,0.0037,0.0008</t>
   </si>
   <si>
-    <t>0.9644,0.0535,0.0008,0.0002</t>
+    <t>0.9644,0.0534,0.0008,0.0002</t>
   </si>
   <si>
     <t>0.9914,0.0101,0.0006,0.0003</t>
@@ -1114,7 +1120,7 @@
     <t>0.9919,0.0013,0.0023,0.0005</t>
   </si>
   <si>
-    <t>0.9905,0.0077,0.0016,0.0007</t>
+    <t>0.9904,0.0077,0.0016,0.0007</t>
   </si>
   <si>
     <t>0.9962,0.0019,0.0005,0.0002</t>
@@ -1141,7 +1147,7 @@
     <t>0.0210,0.0033,0.9807,0.0021</t>
   </si>
   <si>
-    <t>0.9681,0.0001,0.0334,0.0002</t>
+    <t>0.9683,0.0001,0.0332,0.0002</t>
   </si>
   <si>
     <t>0.0433,0.0030,0.9555,0.0014</t>
@@ -1153,31 +1159,31 @@
     <t>0.0001,1.0000,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.3404,0.7235,0.0020,0.0010</t>
-  </si>
-  <si>
-    <t>0.0692,0.9391,0.0373,0.0084</t>
+    <t>0.3412,0.7229,0.0020,0.0010</t>
+  </si>
+  <si>
+    <t>0.0694,0.9390,0.0373,0.0084</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.6508,0.3537,0.0438,0.0038</t>
-  </si>
-  <si>
-    <t>0.1499,0.0301,0.8259,0.0121</t>
+    <t>0.6514,0.3532,0.0437,0.0038</t>
+  </si>
+  <si>
+    <t>0.1503,0.0301,0.8255,0.0121</t>
   </si>
   <si>
     <t>0.0381,0.0086,0.9532,0.0048</t>
   </si>
   <si>
-    <t>0.2574,0.0078,0.7245,0.0042</t>
-  </si>
-  <si>
-    <t>0.1070,0.0164,0.8787,0.0111</t>
-  </si>
-  <si>
-    <t>0.0003,0.5594,0.5356,0.2671</t>
+    <t>0.2579,0.0078,0.7240,0.0042</t>
+  </si>
+  <si>
+    <t>0.1073,0.0164,0.8784,0.0111</t>
+  </si>
+  <si>
+    <t>0.0003,0.5592,0.5356,0.2674</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0012,0.0000</t>
@@ -1186,22 +1192,22 @@
     <t>0.0000,1.0000,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9995,0.0003,0.0036</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0415,0.0003</t>
-  </si>
-  <si>
-    <t>0.0023,0.9899,0.2802,0.0011</t>
-  </si>
-  <si>
-    <t>0.2274,0.7056,0.1060,0.0056</t>
-  </si>
-  <si>
-    <t>0.1802,0.7170,0.1689,0.0188</t>
-  </si>
-  <si>
-    <t>0.9843,0.0009,0.0040,0.0007</t>
+    <t>0.0001,0.9995,0.0003,0.0035</t>
+  </si>
+  <si>
+    <t>0.0002,0.9992,0.0416,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.9899,0.2804,0.0011</t>
+  </si>
+  <si>
+    <t>0.2277,0.7058,0.1059,0.0056</t>
+  </si>
+  <si>
+    <t>0.1804,0.7168,0.1689,0.0188</t>
+  </si>
+  <si>
+    <t>0.9844,0.0009,0.0040,0.0007</t>
   </si>
   <si>
     <t>0.9912,0.0038,0.0003,0.0009</t>
@@ -1225,10 +1231,10 @@
     <t>0.9941,0.0010,0.0014,0.0003</t>
   </si>
   <si>
-    <t>0.0009,0.8049,0.9660,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.4864,0.9914,0.0001</t>
+    <t>0.0009,0.8051,0.9660,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.4867,0.9914,0.0001</t>
   </si>
   <si>
     <t>0.0006,0.0307,0.9971,0.0003</t>
@@ -1237,16 +1243,16 @@
     <t>0.0088,0.0075,0.9909,0.0003</t>
   </si>
   <si>
-    <t>0.9476,0.0012,0.0285,0.0017</t>
-  </si>
-  <si>
-    <t>0.2834,0.4974,0.0540,0.0094</t>
-  </si>
-  <si>
-    <t>0.1475,0.0003,0.9058,0.0014</t>
-  </si>
-  <si>
-    <t>0.4528,0.0075,0.5001,0.0075</t>
+    <t>0.9477,0.0012,0.0284,0.0017</t>
+  </si>
+  <si>
+    <t>0.2840,0.4969,0.0539,0.0094</t>
+  </si>
+  <si>
+    <t>0.1476,0.0003,0.9057,0.0014</t>
+  </si>
+  <si>
+    <t>0.4531,0.0075,0.4998,0.0075</t>
   </si>
   <si>
     <t>0.0143,0.0001,0.0010,0.9968</t>
@@ -1261,13 +1267,13 @@
     <t>0.0037,0.0002,0.0014,0.9993</t>
   </si>
   <si>
-    <t>0.0002,0.9941,0.7954,0.0001</t>
+    <t>0.0002,0.9941,0.7955,0.0001</t>
   </si>
   <si>
     <t>0.9865,0.0016,0.0043,0.0006</t>
   </si>
   <si>
-    <t>0.0086,0.9878,0.0165,0.0125</t>
+    <t>0.0086,0.9877,0.0165,0.0125</t>
   </si>
   <si>
     <t>0.9923,0.0010,0.0022,0.0002</t>
@@ -1282,19 +1288,19 @@
     <t>0.0032,0.0000,0.9991,0.0000</t>
   </si>
   <si>
-    <t>0.0275,0.0000,0.9916,0.0000</t>
+    <t>0.0274,0.0000,0.9916,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0001</t>
   </si>
   <si>
-    <t>0.7117,0.0000,0.1122,0.0032</t>
+    <t>0.7117,0.0000,0.1121,0.0032</t>
   </si>
   <si>
     <t>0.9859,0.0035,0.0030,0.0005</t>
   </si>
   <si>
-    <t>0.6947,0.1529,0.0572,0.0026</t>
+    <t>0.6948,0.1529,0.0572,0.0026</t>
   </si>
   <si>
     <t>0.9872,0.0021,0.0038,0.0006</t>
@@ -1303,16 +1309,16 @@
     <t>0.9405,0.0314,0.0155,0.0018</t>
   </si>
   <si>
-    <t>0.0470,0.9458,0.0186,0.0098</t>
-  </si>
-  <si>
-    <t>0.8612,0.0641,0.0601,0.0032</t>
-  </si>
-  <si>
-    <t>0.7078,0.0173,0.1992,0.0034</t>
-  </si>
-  <si>
-    <t>0.9908,0.0061,0.0014,0.0005</t>
+    <t>0.0471,0.9457,0.0185,0.0098</t>
+  </si>
+  <si>
+    <t>0.8615,0.0641,0.0600,0.0032</t>
+  </si>
+  <si>
+    <t>0.7084,0.0173,0.1986,0.0034</t>
+  </si>
+  <si>
+    <t>0.9908,0.0060,0.0014,0.0005</t>
   </si>
   <si>
     <t>0.9931,0.0050,0.0005,0.0006</t>
@@ -1321,7 +1327,7 @@
     <t>0.9827,0.0032,0.0061,0.0012</t>
   </si>
   <si>
-    <t>0.9896,0.0014,0.0030,0.0004</t>
+    <t>0.9896,0.0014,0.0029,0.0004</t>
   </si>
   <si>
     <t>0.9903,0.0031,0.0022,0.0003</t>
@@ -1336,43 +1342,43 @@
     <t>0.9929,0.0021,0.0014,0.0003</t>
   </si>
   <si>
-    <t>0.7338,0.2605,0.0079,0.0058</t>
-  </si>
-  <si>
-    <t>0.2005,0.8322,0.0148,0.0056</t>
-  </si>
-  <si>
-    <t>0.7047,0.3479,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.8879,0.0156,0.0786,0.0017</t>
+    <t>0.7339,0.2604,0.0080,0.0058</t>
+  </si>
+  <si>
+    <t>0.2008,0.8319,0.0147,0.0056</t>
+  </si>
+  <si>
+    <t>0.7049,0.3477,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.8878,0.0156,0.0786,0.0017</t>
   </si>
   <si>
     <t>0.9893,0.0065,0.0020,0.0004</t>
   </si>
   <si>
-    <t>0.8382,0.0403,0.0929,0.0031</t>
+    <t>0.8386,0.0403,0.0925,0.0031</t>
   </si>
   <si>
     <t>0.9864,0.0021,0.0051,0.0004</t>
   </si>
   <si>
-    <t>0.9129,0.0764,0.0218,0.0053</t>
+    <t>0.9130,0.0763,0.0218,0.0053</t>
   </si>
   <si>
     <t>0.0064,0.0064,0.9961,0.0004</t>
   </si>
   <si>
-    <t>0.8274,0.0704,0.0797,0.0024</t>
+    <t>0.8276,0.0704,0.0796,0.0024</t>
   </si>
   <si>
     <t>0.0011,0.0005,0.9991,0.0001</t>
   </si>
   <si>
-    <t>0.0002,0.1362,0.9958,0.0006</t>
-  </si>
-  <si>
-    <t>0.0078,0.0022,0.9937,0.0014</t>
+    <t>0.0002,0.1364,0.9958,0.0006</t>
+  </si>
+  <si>
+    <t>0.0079,0.0022,0.9937,0.0014</t>
   </si>
   <si>
     <t>0.0020,0.1573,0.9848,0.0006</t>
@@ -1387,91 +1393,91 @@
     <t>0.0180,0.0015,0.9849,0.0008</t>
   </si>
   <si>
-    <t>0.1281,0.0049,0.8725,0.0024</t>
-  </si>
-  <si>
-    <t>0.2041,0.0004,0.8696,0.0003</t>
-  </si>
-  <si>
-    <t>0.4642,0.0237,0.4557,0.0080</t>
+    <t>0.1282,0.0049,0.8724,0.0024</t>
+  </si>
+  <si>
+    <t>0.2042,0.0004,0.8696,0.0003</t>
+  </si>
+  <si>
+    <t>0.4647,0.0237,0.4551,0.0080</t>
   </si>
   <si>
     <t>0.0428,0.0100,0.9506,0.0034</t>
   </si>
   <si>
-    <t>0.0151,0.0218,0.9668,0.0009</t>
+    <t>0.0151,0.0218,0.9669,0.0009</t>
   </si>
   <si>
     <t>0.0688,0.0024,0.9451,0.0012</t>
   </si>
   <si>
-    <t>0.0966,0.0059,0.9036,0.0051</t>
-  </si>
-  <si>
-    <t>0.4923,0.0251,0.4248,0.0054</t>
-  </si>
-  <si>
-    <t>0.0503,0.9734,0.0043,0.0002</t>
+    <t>0.0967,0.0059,0.9035,0.0051</t>
+  </si>
+  <si>
+    <t>0.4929,0.0252,0.4240,0.0054</t>
+  </si>
+  <si>
+    <t>0.0504,0.9734,0.0043,0.0002</t>
   </si>
   <si>
     <t>0.0047,0.9974,0.0012,0.0002</t>
   </si>
   <si>
-    <t>0.1017,0.9409,0.0030,0.0007</t>
-  </si>
-  <si>
-    <t>0.9750,0.0196,0.0038,0.0004</t>
-  </si>
-  <si>
-    <t>0.6614,0.4419,0.0047,0.0008</t>
-  </si>
-  <si>
-    <t>0.1421,0.8544,0.0142,0.0023</t>
-  </si>
-  <si>
-    <t>0.9510,0.0021,0.0233,0.0013</t>
-  </si>
-  <si>
-    <t>0.2174,0.0232,0.7340,0.0216</t>
-  </si>
-  <si>
-    <t>0.1726,0.0020,0.8201,0.0132</t>
-  </si>
-  <si>
-    <t>0.5176,0.0160,0.3614,0.0050</t>
+    <t>0.1019,0.9408,0.0030,0.0007</t>
+  </si>
+  <si>
+    <t>0.9750,0.0195,0.0038,0.0004</t>
+  </si>
+  <si>
+    <t>0.6615,0.4419,0.0047,0.0008</t>
+  </si>
+  <si>
+    <t>0.1422,0.8544,0.0142,0.0023</t>
+  </si>
+  <si>
+    <t>0.9511,0.0021,0.0232,0.0013</t>
+  </si>
+  <si>
+    <t>0.2182,0.0232,0.7332,0.0217</t>
+  </si>
+  <si>
+    <t>0.1728,0.0020,0.8199,0.0132</t>
+  </si>
+  <si>
+    <t>0.5185,0.0160,0.3606,0.0050</t>
   </si>
   <si>
     <t>0.0075,0.0006,0.9941,0.0005</t>
   </si>
   <si>
-    <t>0.0739,0.0059,0.9433,0.0024</t>
-  </si>
-  <si>
-    <t>0.0334,0.0542,0.9255,0.0011</t>
+    <t>0.0741,0.0059,0.9432,0.0024</t>
+  </si>
+  <si>
+    <t>0.0334,0.0542,0.9254,0.0011</t>
   </si>
   <si>
     <t>0.0069,0.0027,0.9929,0.0004</t>
   </si>
   <si>
-    <t>0.0216,0.0184,0.9650,0.0004</t>
-  </si>
-  <si>
-    <t>0.9890,0.0016,0.0034,0.0003</t>
+    <t>0.0217,0.0185,0.9650,0.0004</t>
+  </si>
+  <si>
+    <t>0.9890,0.0016,0.0033,0.0003</t>
   </si>
   <si>
     <t>0.9669,0.0202,0.0078,0.0019</t>
   </si>
   <si>
-    <t>0.9233,0.0628,0.0070,0.0044</t>
-  </si>
-  <si>
-    <t>0.9879,0.0128,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.9537,0.0351,0.0110,0.0033</t>
-  </si>
-  <si>
-    <t>0.9723,0.0251,0.0041,0.0015</t>
+    <t>0.9234,0.0628,0.0070,0.0044</t>
+  </si>
+  <si>
+    <t>0.9879,0.0127,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9537,0.0350,0.0110,0.0033</t>
+  </si>
+  <si>
+    <t>0.9724,0.0251,0.0040,0.0015</t>
   </si>
   <si>
     <t>0.9754,0.0131,0.0062,0.0020</t>
@@ -1483,10 +1489,10 @@
     <t>0.0122,0.0028,0.9922,0.0012</t>
   </si>
   <si>
-    <t>0.1021,0.0313,0.8881,0.0035</t>
-  </si>
-  <si>
-    <t>0.4336,0.0088,0.5504,0.0125</t>
+    <t>0.1023,0.0313,0.8879,0.0035</t>
+  </si>
+  <si>
+    <t>0.4340,0.0089,0.5498,0.0125</t>
   </si>
   <si>
     <t>0.0010,0.0003,0.9991,0.0001</t>
@@ -1498,28 +1504,25 @@
     <t>0.0060,0.0443,0.9727,0.0019</t>
   </si>
   <si>
-    <t>0.0001,0.0000,1.0000,0.0000</t>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
     <t>0.0340,0.0109,0.9580,0.0016</t>
   </si>
   <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
     <t>0.0039,0.0032,0.9949,0.0005</t>
   </si>
   <si>
-    <t>0.0425,0.0194,0.9386,0.0057</t>
-  </si>
-  <si>
-    <t>0.7859,0.0009,0.2098,0.0021</t>
-  </si>
-  <si>
-    <t>0.2814,0.0008,0.6786,0.0080</t>
-  </si>
-  <si>
-    <t>0.9610,0.0077,0.0137,0.0010</t>
+    <t>0.0425,0.0194,0.9386,0.0058</t>
+  </si>
+  <si>
+    <t>0.7862,0.0009,0.2093,0.0021</t>
+  </si>
+  <si>
+    <t>0.2819,0.0008,0.6779,0.0080</t>
+  </si>
+  <si>
+    <t>0.9611,0.0077,0.0137,0.0010</t>
   </si>
   <si>
     <t>0.9931,0.0044,0.0008,0.0002</t>
@@ -1531,13 +1534,13 @@
     <t>0.9907,0.0055,0.0016,0.0004</t>
   </si>
   <si>
-    <t>0.9160,0.0719,0.0074,0.0017</t>
+    <t>0.9159,0.0720,0.0074,0.0017</t>
   </si>
   <si>
     <t>0.9906,0.0022,0.0022,0.0003</t>
   </si>
   <si>
-    <t>0.9789,0.0186,0.0025,0.0006</t>
+    <t>0.9789,0.0185,0.0025,0.0006</t>
   </si>
   <si>
     <t>0.9885,0.0108,0.0014,0.0008</t>
@@ -1555,22 +1558,22 @@
     <t>0.0022,0.0042,0.9972,0.0002</t>
   </si>
   <si>
-    <t>0.0322,0.0361,0.9086,0.0021</t>
+    <t>0.0322,0.0360,0.9087,0.0021</t>
   </si>
   <si>
     <t>0.0211,0.0010,0.9852,0.0005</t>
   </si>
   <si>
-    <t>0.6778,0.0281,0.0731,0.0272</t>
-  </si>
-  <si>
-    <t>0.0929,0.0223,0.8493,0.0098</t>
+    <t>0.6784,0.0282,0.0728,0.0271</t>
+  </si>
+  <si>
+    <t>0.0932,0.0224,0.8488,0.0098</t>
   </si>
   <si>
     <t>0.0040,0.0008,0.9961,0.0009</t>
   </si>
   <si>
-    <t>0.8878,0.0002,0.0077,0.0347</t>
+    <t>0.8879,0.0002,0.0077,0.0347</t>
   </si>
   <si>
     <t>0.0006,0.0021,0.0002,0.9998</t>
@@ -1585,7 +1588,7 @@
     <t>0.0001,0.0004,0.0022,0.9999</t>
   </si>
   <si>
-    <t>0.7033,0.0034,0.0177,0.2788</t>
+    <t>0.7036,0.0034,0.0177,0.2786</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +1974,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1985,7 +1988,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1999,7 +2002,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2013,7 +2016,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2027,7 +2030,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2041,7 +2044,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2055,7 +2058,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2069,7 +2072,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2083,7 +2086,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2097,7 +2100,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2111,7 +2114,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2125,7 +2128,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2139,7 +2142,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2153,7 +2156,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2167,7 +2170,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2181,7 +2184,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2192,10 +2195,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2206,10 +2209,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2220,10 +2223,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2234,10 +2237,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2248,10 +2251,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2262,10 +2265,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2279,7 +2282,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2293,7 +2296,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2307,7 +2310,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2321,7 +2324,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2335,7 +2338,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2349,7 +2352,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2363,7 +2366,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2377,7 +2380,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2391,7 +2394,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2405,7 +2408,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2419,7 +2422,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2433,7 +2436,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2447,7 +2450,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2458,10 +2461,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2472,10 +2475,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2486,10 +2489,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2503,7 +2506,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2517,7 +2520,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2531,7 +2534,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2545,7 +2548,7 @@
         <v>266</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2556,10 +2559,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2573,7 +2576,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2584,10 +2587,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2598,10 +2601,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2612,10 +2615,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2626,10 +2629,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2643,7 +2646,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2657,7 +2660,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2671,7 +2674,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2685,7 +2688,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2699,7 +2702,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2713,7 +2716,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2727,7 +2730,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2741,7 +2744,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2755,7 +2758,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2769,7 +2772,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2783,7 +2786,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2797,7 +2800,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2811,7 +2814,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2822,10 +2825,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2839,7 +2842,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2853,7 +2856,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2864,10 +2867,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2881,7 +2884,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2892,10 +2895,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2906,10 +2909,10 @@
         <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2923,7 +2926,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2937,7 +2940,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2951,7 +2954,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2962,10 +2965,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2976,10 +2979,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2990,10 +2993,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3004,10 +3007,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3021,7 +3024,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3035,7 +3038,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3049,7 +3052,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3063,7 +3066,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3077,7 +3080,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3091,7 +3094,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3102,10 +3105,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3116,10 +3119,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3130,10 +3133,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3144,10 +3147,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3158,10 +3161,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3172,10 +3175,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3189,7 +3192,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3203,7 +3206,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3217,7 +3220,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3231,7 +3234,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3245,7 +3248,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3259,7 +3262,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3273,7 +3276,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3287,7 +3290,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3301,7 +3304,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3315,7 +3318,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3329,7 +3332,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3343,7 +3346,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3357,7 +3360,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3371,7 +3374,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3385,7 +3388,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3399,7 +3402,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3413,7 +3416,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3427,7 +3430,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3441,7 +3444,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3455,7 +3458,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3466,10 +3469,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3480,10 +3483,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D110" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3494,10 +3497,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3508,10 +3511,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3522,10 +3525,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D113" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3536,10 +3539,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D114" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3553,7 +3556,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3567,7 +3570,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3581,7 +3584,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3595,7 +3598,7 @@
         <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3609,7 +3612,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3620,10 +3623,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3634,10 +3637,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3648,10 +3651,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3662,10 +3665,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3676,10 +3679,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3690,10 +3693,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3704,10 +3707,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3718,10 +3721,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3735,7 +3738,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3749,7 +3752,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3763,7 +3766,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3777,7 +3780,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3791,7 +3794,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3805,7 +3808,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3819,7 +3822,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3833,7 +3836,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3844,10 +3847,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3861,7 +3864,7 @@
         <v>266</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3875,7 +3878,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3889,7 +3892,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3903,7 +3906,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3914,10 +3917,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3931,7 +3934,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3942,10 +3945,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3959,7 +3962,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3973,7 +3976,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3987,7 +3990,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4001,7 +4004,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4012,10 +4015,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4029,7 +4032,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4040,10 +4043,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4057,7 +4060,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4068,10 +4071,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4085,7 +4088,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4099,7 +4102,7 @@
         <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4113,7 +4116,7 @@
         <v>266</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4127,7 +4130,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4141,7 +4144,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4155,7 +4158,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4169,7 +4172,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4183,7 +4186,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4197,7 +4200,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4208,10 +4211,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4225,7 +4228,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4239,7 +4242,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4253,7 +4256,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4267,7 +4270,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4281,7 +4284,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4295,7 +4298,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4309,7 +4312,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4323,7 +4326,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4337,7 +4340,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4351,7 +4354,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4365,7 +4368,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4376,10 +4379,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4393,7 +4396,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4407,7 +4410,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4421,7 +4424,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4435,7 +4438,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4449,7 +4452,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4463,7 +4466,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4477,7 +4480,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4491,7 +4494,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4505,7 +4508,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4519,7 +4522,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4533,7 +4536,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4547,7 +4550,7 @@
         <v>266</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4561,7 +4564,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4575,7 +4578,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4589,7 +4592,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4603,7 +4606,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4617,7 +4620,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4628,10 +4631,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4645,7 +4648,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4659,7 +4662,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4673,7 +4676,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4687,7 +4690,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4698,10 +4701,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4712,10 +4715,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4726,10 +4729,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4740,10 +4743,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4757,7 +4760,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4771,7 +4774,7 @@
         <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4782,10 +4785,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4799,7 +4802,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4813,7 +4816,7 @@
         <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4827,7 +4830,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4841,7 +4844,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4855,7 +4858,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4869,7 +4872,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4883,7 +4886,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4897,7 +4900,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4911,7 +4914,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4925,7 +4928,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4939,7 +4942,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4953,7 +4956,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4967,7 +4970,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4981,7 +4984,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4995,7 +4998,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5009,7 +5012,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5023,7 +5026,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5037,7 +5040,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5051,7 +5054,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5065,7 +5068,7 @@
         <v>266</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5079,7 +5082,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5093,7 +5096,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5107,7 +5110,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5121,7 +5124,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5135,7 +5138,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5163,7 +5166,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5177,7 +5180,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5191,7 +5194,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5205,7 +5208,7 @@
         <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5219,7 +5222,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5233,7 +5236,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5247,7 +5250,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5261,7 +5264,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5275,7 +5278,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5289,7 +5292,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5303,7 +5306,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5317,7 +5320,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5331,7 +5334,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5345,7 +5348,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5359,7 +5362,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5373,7 +5376,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5387,7 +5390,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5401,7 +5404,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5415,7 +5418,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5429,7 +5432,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5443,7 +5446,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5457,7 +5460,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5471,7 +5474,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5485,7 +5488,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5499,7 +5502,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5513,7 +5516,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5527,7 +5530,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
